--- a/ig/DM-SIDOBA/CodeSystem-tre-r412-niveau-diplome.xlsx
+++ b/ig/DM-SIDOBA/CodeSystem-tre-r412-niveau-diplome.xlsx
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Niveau de diplôme.</t>
+    <t>Niveau de diplôme permettant d'indiquer le type de formation nécessaire pour occuper un poste dans le monde professionnel.</t>
   </si>
   <si>
     <t>Purpose</t>
